--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487087_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487087_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. ETXEBERRIA AGUIRREZABALA</t>
+          <t>E. HUIZI ZUBELDIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3479</v>
+        <v>4.9997</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0009</v>
+        <v>4.5748</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3471</v>
+        <v>0.4249</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3002</v>
+        <v>5.2126</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.222</v>
+        <v>0.0146</v>
       </c>
       <c r="I2" t="n">
-        <v>5.5222</v>
+        <v>5.1981</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6752</v>
+        <v>7.8354</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.2669</v>
+        <v>2.0647</v>
       </c>
       <c r="L2" t="n">
-        <v>5.9421</v>
+        <v>5.7707</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.375</v>
+        <v>-2.6228</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9550999999999999</v>
+        <v>-2.0501</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4199</v>
+        <v>-0.5727</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3511</v>
+        <v>-0.193</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3161</v>
+        <v>2.7021</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0827</v>
+        <v>-0.6339</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1652</v>
+        <v>-0.6514</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2479</v>
+        <v>0.0175</v>
       </c>
       <c r="V2" t="n">
         <v>0.614</v>
       </c>
       <c r="W2" t="n">
-        <v>2.4559</v>
+        <v>0.2859</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.842</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. HUIZI ZUBELDIA</t>
+          <t>A. ARMENDARIZ LOPEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9402</v>
+        <v>4.8399</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2744</v>
+        <v>3.9856</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.8542999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>5.2126</v>
+        <v>3.5113</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0146</v>
+        <v>-1.2326</v>
       </c>
       <c r="I3" t="n">
-        <v>5.1981</v>
+        <v>4.744</v>
       </c>
       <c r="J3" t="n">
-        <v>7.8354</v>
+        <v>5.5802</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0647</v>
+        <v>0.4035</v>
       </c>
       <c r="L3" t="n">
-        <v>5.7707</v>
+        <v>5.1767</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.6228</v>
+        <v>-2.0689</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.0501</v>
+        <v>-1.6361</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5727</v>
+        <v>-0.4327</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.193</v>
+        <v>1.9301</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7021</v>
+        <v>2.8951</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6934</v>
+        <v>-0.3156</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9518</v>
+        <v>-0.6296</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2584</v>
+        <v>0.3139</v>
       </c>
       <c r="V3" t="n">
-        <v>0.614</v>
+        <v>-0.2859</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3281</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ARMENDARIZ LOPEZ</t>
+          <t>B. ETXEBERRIA AGUIRREZABALA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2857</v>
+        <v>4.6519</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4849</v>
+        <v>5.0009</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8008</v>
+        <v>-0.3489</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5113</v>
+        <v>2.3002</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2326</v>
+        <v>-3.222</v>
       </c>
       <c r="I4" t="n">
-        <v>4.744</v>
+        <v>5.5222</v>
       </c>
       <c r="J4" t="n">
-        <v>5.5802</v>
+        <v>3.6752</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4035</v>
+        <v>-2.2669</v>
       </c>
       <c r="L4" t="n">
-        <v>5.1767</v>
+        <v>5.9421</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0689</v>
+        <v>-1.375</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6361</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4327</v>
+        <v>-0.4199</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9301</v>
+        <v>1.3511</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.965</v>
       </c>
       <c r="R4" t="n">
-        <v>2.8951</v>
+        <v>2.3161</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8699</v>
+        <v>0.3867</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1303</v>
+        <v>-0.1652</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2604</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2859</v>
+        <v>0.614</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.4559</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2859</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. IRASTORZA EZKIAGA</t>
+          <t>E. ERRASTI URANGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2623</v>
+        <v>1.2621</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1506</v>
+        <v>0.4736</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1117</v>
+        <v>0.7885</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4492</v>
+        <v>1.0205</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0195</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4687</v>
+        <v>0.4998</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1968</v>
+        <v>1.5546</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3828</v>
+        <v>1.4489</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.1057</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7476</v>
+        <v>-0.5341</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4023</v>
+        <v>-0.9283</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.3941</v>
       </c>
       <c r="P5" t="n">
-        <v>0.193</v>
+        <v>0.386</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.965</v>
       </c>
       <c r="R5" t="n">
-        <v>1.158</v>
+        <v>1.3511</v>
       </c>
       <c r="S5" t="n">
-        <v>0.62</v>
+        <v>-0.1444</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9188</v>
+        <v>-0.116</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2988</v>
+        <v>-0.0284</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. ERRASTI URANGA</t>
+          <t>U. CONDE LAKUNTZA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0152</v>
+        <v>0.6117</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1732</v>
+        <v>0.7343</v>
       </c>
       <c r="F6" t="n">
-        <v>0.842</v>
+        <v>-0.1226</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0205</v>
+        <v>-0.4531</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5207000000000001</v>
+        <v>-0.4367</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4998</v>
+        <v>-0.0164</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5546</v>
+        <v>0.8285</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4489</v>
+        <v>0.6985</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1057</v>
+        <v>0.13</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5341</v>
+        <v>-1.2817</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9283</v>
+        <v>-1.1353</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3941</v>
+        <v>-0.1464</v>
       </c>
       <c r="P6" t="n">
-        <v>0.386</v>
+        <v>1.158</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3511</v>
+        <v>1.158</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3913</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4164</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0251</v>
+        <v>0.001</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ALDA IRAOLA</t>
+          <t>A. IRASTORZA EZKIAGA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2825</v>
+        <v>0.5682</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6183999999999999</v>
+        <v>0.3494</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9009</v>
+        <v>0.2188</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6219</v>
+        <v>0.4492</v>
       </c>
       <c r="H7" t="n">
-        <v>0.739</v>
+        <v>-1.0195</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1171</v>
+        <v>1.4687</v>
       </c>
       <c r="J7" t="n">
-        <v>0.882</v>
+        <v>1.1968</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3868</v>
+        <v>0.3828</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5048</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2601</v>
+        <v>-0.7476</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6478</v>
+        <v>-1.4023</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3877</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>1.158</v>
+        <v>0.193</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1231</v>
+        <v>1.158</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2116</v>
+        <v>-0.074</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5354</v>
+        <v>0.1177</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6762</v>
+        <v>-0.1917</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>U. CONDE LAKUNTZA</t>
+          <t>A. ALDA IRAOLA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1299</v>
+        <v>0.4699</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2336</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3635</v>
+        <v>1.0883</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4531</v>
+        <v>0.6219</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4367</v>
+        <v>0.739</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0164</v>
+        <v>-0.1171</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8285</v>
+        <v>0.882</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6985</v>
+        <v>1.3868</v>
       </c>
       <c r="L8" t="n">
-        <v>0.13</v>
+        <v>-0.5048</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2817</v>
+        <v>-0.2601</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1353</v>
+        <v>-0.6478</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1464</v>
+        <v>0.3877</v>
       </c>
       <c r="P8" t="n">
         <v>1.158</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R8" t="n">
-        <v>1.158</v>
+        <v>2.1231</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8348</v>
+        <v>-1.0242</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5949</v>
+        <v>-0.5354</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2399</v>
+        <v>-0.4888</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4776</v>
+        <v>-0.2169</v>
       </c>
       <c r="E9" t="n">
-        <v>1.872</v>
+        <v>1.9721</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3496</v>
+        <v>-2.189</v>
       </c>
       <c r="G9" t="n">
         <v>0.9291</v>
@@ -1156,13 +1156,13 @@
         <v>0.579</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4719</v>
+        <v>-0.2112</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1785</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2935</v>
+        <v>-0.1329</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5138</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8745000000000001</v>
+        <v>-0.8477</v>
       </c>
       <c r="E10" t="n">
         <v>-0.119</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.7287</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6805</v>
@@ -1234,13 +1234,13 @@
         <v>0.193</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1011</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="T10" t="n">
         <v>-0.119</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2859</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. URTXULUTEGI NAVARRI</t>
+          <t>U. PEREZ SANZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5979</v>
+        <v>-2.0224</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0029</v>
+        <v>-2.6562</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.595</v>
+        <v>0.6338</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5891</v>
+        <v>-0.5847</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.7273</v>
+        <v>0.3778</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1381</v>
+        <v>-0.9625</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2808</v>
+        <v>1.2037</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9576</v>
+        <v>1.7335</v>
       </c>
       <c r="L11" t="n">
-        <v>2.2385</v>
+        <v>-0.5298</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.87</v>
+        <v>-1.7884</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.7697</v>
+        <v>-1.3557</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1003</v>
+        <v>-0.4327</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.5091</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q11" t="n">
         <v>-3.8602</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3511</v>
+        <v>2.5091</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2724</v>
+        <v>-0.7007</v>
       </c>
       <c r="T11" t="n">
-        <v>1.3484</v>
+        <v>-0.6137</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.076</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>1.228</v>
+        <v>0.614</v>
       </c>
       <c r="W11" t="n">
-        <v>1.228</v>
+        <v>0.614</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>U. PEREZ SANZ</t>
+          <t>J. URTXULUTEGI NAVARRI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0958</v>
+        <v>-2.3583</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7563</v>
+        <v>-1.0043</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6605</v>
+        <v>-1.354</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5847</v>
+        <v>-1.5891</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3778</v>
+        <v>-2.7273</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9625</v>
+        <v>1.1381</v>
       </c>
       <c r="J12" t="n">
-        <v>1.2037</v>
+        <v>1.2808</v>
       </c>
       <c r="K12" t="n">
-        <v>1.7335</v>
+        <v>-0.9576</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5298</v>
+        <v>2.2385</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7884</v>
+        <v>-2.87</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3557</v>
+        <v>-1.7697</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4327</v>
+        <v>-1.1003</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.3511</v>
+        <v>-2.5091</v>
       </c>
       <c r="Q12" t="n">
         <v>-3.8602</v>
       </c>
       <c r="R12" t="n">
-        <v>2.5091</v>
+        <v>1.3511</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.774</v>
+        <v>0.5119</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7139</v>
+        <v>0.347</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0602</v>
+        <v>0.1649</v>
       </c>
       <c r="V12" t="n">
-        <v>0.614</v>
+        <v>1.228</v>
       </c>
       <c r="W12" t="n">
-        <v>0.614</v>
+        <v>1.228</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1426,16 +1426,16 @@
         <v>11.9581</v>
       </c>
       <c r="E13" t="n">
-        <v>12.693</v>
+        <v>12.6928</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7348000000000002</v>
+        <v>-0.7346000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>10.7374</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.877300000000001</v>
+        <v>-6.8773</v>
       </c>
       <c r="I13" t="n">
         <v>17.61480000000001</v>
@@ -1444,10 +1444,10 @@
         <v>26.0876</v>
       </c>
       <c r="K13" t="n">
-        <v>5.5773</v>
+        <v>5.577300000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>20.51049999999999</v>
+        <v>20.5105</v>
       </c>
       <c r="M13" t="n">
         <v>-15.3504</v>
@@ -1468,13 +1468,13 @@
         <v>18.3357</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.3729</v>
+        <v>-2.372999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.5382</v>
+        <v>-2.5381</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1650000000000001</v>
+        <v>0.1651</v>
       </c>
       <c r="V13" t="n">
         <v>0.6984999999999998</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0579</v>
+        <v>2.2314</v>
       </c>
       <c r="E14" t="n">
-        <v>1.338</v>
+        <v>1.5383</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7199</v>
+        <v>0.6931</v>
       </c>
       <c r="G14" t="n">
         <v>0.4868</v>
@@ -1546,13 +1546,13 @@
         <v>1.7371</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1659</v>
+        <v>0.0076</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4759</v>
+        <v>-0.2756</v>
       </c>
       <c r="U14" t="n">
-        <v>0.31</v>
+        <v>0.2832</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. DIALLO TOURE</t>
+          <t>P. SOUZA FIGUEIREDO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3933</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2707</v>
+        <v>2.8224</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1226</v>
+        <v>-2.1001</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3361</v>
+        <v>-1.0324</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2915</v>
+        <v>0.6105</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9554</v>
+        <v>-1.6429</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3775</v>
+        <v>1.8901</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6857</v>
+        <v>1.3452</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6919</v>
+        <v>0.5448</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0415</v>
+        <v>-2.9225</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3942</v>
+        <v>-0.7347</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.6473</v>
+        <v>-2.1878</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.7371</v>
+        <v>-0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R15" t="n">
-        <v>1.158</v>
+        <v>1.9301</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5084</v>
+        <v>0.2409</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5024</v>
+        <v>0.1207</v>
       </c>
       <c r="U15" t="n">
-        <v>1.006</v>
+        <v>0.1203</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2859</v>
+        <v>1.5138</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2859</v>
+        <v>2.7418</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. SOUZA FIGUEIREDO</t>
+          <t>C. DIALLO TOURE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0089</v>
+        <v>0.6715</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3231</v>
+        <v>0.8701</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.3142</v>
+        <v>-0.1986</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0324</v>
+        <v>1.3361</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6105</v>
+        <v>2.2915</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.6429</v>
+        <v>-0.9554</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8901</v>
+        <v>3.3775</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3452</v>
+        <v>2.6857</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5448</v>
+        <v>0.6919</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.9225</v>
+        <v>-2.0415</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7347</v>
+        <v>-0.3942</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.1878</v>
+        <v>-1.6473</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9301</v>
+        <v>1.158</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5275</v>
+        <v>0.7866</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6214</v>
+        <v>0.1018</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0939</v>
+        <v>0.6848</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5138</v>
+        <v>0.2859</v>
       </c>
       <c r="W16" t="n">
-        <v>2.7418</v>
+        <v>0.2859</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9456</v>
+        <v>0.2714</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4167</v>
+        <v>1.7157</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4711</v>
+        <v>-1.4444</v>
       </c>
       <c r="G17" t="n">
         <v>-2.143</v>
@@ -1780,13 +1780,13 @@
         <v>2.1231</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2936</v>
+        <v>0.6194</v>
       </c>
       <c r="T17" t="n">
-        <v>1.051</v>
+        <v>0.35</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2426</v>
+        <v>0.2693</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3281</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4745</v>
+        <v>-0.4943</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7683</v>
+        <v>-0.8685</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2939</v>
+        <v>0.3742</v>
       </c>
       <c r="G19" t="n">
         <v>-1.4627</v>
@@ -1936,13 +1936,13 @@
         <v>1.5441</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4092</v>
+        <v>0.3893</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1917</v>
+        <v>0.0916</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2175</v>
+        <v>0.2978</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0496</v>
+        <v>-2.4581</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6946</v>
+        <v>-1.5945</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.355</v>
+        <v>-0.8636</v>
       </c>
       <c r="G20" t="n">
         <v>-2.0833</v>
@@ -2014,13 +2014,13 @@
         <v>2.1231</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8057</v>
+        <v>0.3973</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1057</v>
+        <v>-0.0056</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9115</v>
+        <v>0.4028</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.5345</v>
+        <v>-3.9267</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3709</v>
+        <v>-0.8702</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1636</v>
+        <v>-3.0565</v>
       </c>
       <c r="G21" t="n">
         <v>-2.1749</v>
@@ -2092,13 +2092,13 @@
         <v>1.3511</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5526</v>
+        <v>0.0552</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6544</v>
+        <v>-0.1537</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1018</v>
+        <v>0.2089</v>
       </c>
       <c r="V21" t="n">
         <v>-1.228</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6047</v>
+        <v>-4.104</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2626</v>
+        <v>-0.7619</v>
       </c>
       <c r="F22" t="n">
         <v>-3.342</v>
@@ -2170,10 +2170,10 @@
         <v>1.3511</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8606</v>
+        <v>-0.3599</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9518</v>
+        <v>-0.4511</v>
       </c>
       <c r="U22" t="n">
         <v>0.0912</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.2936</v>
+        <v>-4.4647</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5174</v>
+        <v>-2.1168</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7762</v>
+        <v>-2.3479</v>
       </c>
       <c r="G23" t="n">
         <v>-3.3154</v>
@@ -2248,13 +2248,13 @@
         <v>2.1231</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.2366</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3437</v>
+        <v>0.0569</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2485</v>
+        <v>0.1798</v>
       </c>
       <c r="V23" t="n">
         <v>-0.614</v>
@@ -2284,10 +2284,10 @@
         <v>-11.9582</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7347000000000015</v>
+        <v>0.734599999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-12.6927</v>
+        <v>-12.6928</v>
       </c>
       <c r="G24" t="n">
         <v>-10.7376</v>
@@ -2326,13 +2326,13 @@
         <v>15.4408</v>
       </c>
       <c r="S24" t="n">
-        <v>2.3731</v>
+        <v>2.373</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1650000000000001</v>
+        <v>-0.165</v>
       </c>
       <c r="U24" t="n">
-        <v>2.5382</v>
+        <v>2.5381</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6984999999999999</v>
